--- a/artfynd/A 16667-2025 artfynd.xlsx
+++ b/artfynd/A 16667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128500925</v>
       </c>
       <c r="B2" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128501038</v>
       </c>
       <c r="B3" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128501034</v>
       </c>
       <c r="B4" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128501302</v>
       </c>
       <c r="B5" t="n">
-        <v>92404</v>
+        <v>92410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128500895</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128500934</v>
       </c>
       <c r="B7" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128501107</v>
       </c>
       <c r="B8" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16667-2025 artfynd.xlsx
+++ b/artfynd/A 16667-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>128501034</v>
       </c>
       <c r="B4" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128501302</v>
       </c>
       <c r="B5" t="n">
-        <v>92410</v>
+        <v>92416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128500934</v>
       </c>
       <c r="B7" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16667-2025 artfynd.xlsx
+++ b/artfynd/A 16667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128500925</v>
       </c>
       <c r="B2" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128501038</v>
       </c>
       <c r="B3" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128501034</v>
       </c>
       <c r="B4" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128501302</v>
       </c>
       <c r="B5" t="n">
-        <v>92416</v>
+        <v>92418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128500895</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128500934</v>
       </c>
       <c r="B7" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128501107</v>
       </c>
       <c r="B8" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16667-2025 artfynd.xlsx
+++ b/artfynd/A 16667-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>128501034</v>
       </c>
       <c r="B4" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128501302</v>
       </c>
       <c r="B5" t="n">
-        <v>92418</v>
+        <v>92419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128500934</v>
       </c>
       <c r="B7" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16667-2025 artfynd.xlsx
+++ b/artfynd/A 16667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128500925</v>
       </c>
       <c r="B2" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128501038</v>
       </c>
       <c r="B3" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128501034</v>
       </c>
       <c r="B4" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128501302</v>
       </c>
       <c r="B5" t="n">
-        <v>92419</v>
+        <v>92446</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128500895</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128500934</v>
       </c>
       <c r="B7" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128501107</v>
       </c>
       <c r="B8" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16667-2025 artfynd.xlsx
+++ b/artfynd/A 16667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128500925</v>
       </c>
       <c r="B2" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128501038</v>
       </c>
       <c r="B3" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128501034</v>
       </c>
       <c r="B4" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128501302</v>
       </c>
       <c r="B5" t="n">
-        <v>92446</v>
+        <v>92451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128500895</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128500934</v>
       </c>
       <c r="B7" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128501107</v>
       </c>
       <c r="B8" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16667-2025 artfynd.xlsx
+++ b/artfynd/A 16667-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>128501034</v>
       </c>
       <c r="B4" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128501302</v>
       </c>
       <c r="B5" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128500934</v>
       </c>
       <c r="B7" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16667-2025 artfynd.xlsx
+++ b/artfynd/A 16667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128500925</v>
       </c>
       <c r="B2" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128501038</v>
       </c>
       <c r="B3" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128501034</v>
       </c>
       <c r="B4" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128501302</v>
       </c>
       <c r="B5" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128500895</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128500934</v>
       </c>
       <c r="B7" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128501107</v>
       </c>
       <c r="B8" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16667-2025 artfynd.xlsx
+++ b/artfynd/A 16667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128500925</v>
       </c>
       <c r="B2" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128501038</v>
       </c>
       <c r="B3" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128501034</v>
       </c>
       <c r="B4" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128501302</v>
       </c>
       <c r="B5" t="n">
-        <v>92460</v>
+        <v>92465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128500895</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128500934</v>
       </c>
       <c r="B7" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128501107</v>
       </c>
       <c r="B8" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16667-2025 artfynd.xlsx
+++ b/artfynd/A 16667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128500925</v>
       </c>
       <c r="B2" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128501038</v>
       </c>
       <c r="B3" t="n">
-        <v>82892</v>
+        <v>82897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128501034</v>
       </c>
       <c r="B4" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128501302</v>
       </c>
       <c r="B5" t="n">
-        <v>92468</v>
+        <v>92473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128500895</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128500934</v>
       </c>
       <c r="B7" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128501107</v>
       </c>
       <c r="B8" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16667-2025 artfynd.xlsx
+++ b/artfynd/A 16667-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128500925</v>
+        <v>128501038</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372575</v>
+        <v>372611</v>
       </c>
       <c r="R2" t="n">
-        <v>7026363</v>
+        <v>7026315</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128501038</v>
+        <v>128500925</v>
       </c>
       <c r="B3" t="n">
-        <v>82897</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372611</v>
+        <v>372575</v>
       </c>
       <c r="R3" t="n">
-        <v>7026315</v>
+        <v>7026363</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128501034</v>
+        <v>128500934</v>
       </c>
       <c r="B4" t="n">
-        <v>91538</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372611</v>
+        <v>372572</v>
       </c>
       <c r="R4" t="n">
-        <v>7026315</v>
+        <v>7026354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>128501302</v>
       </c>
       <c r="B5" t="n">
-        <v>92473</v>
+        <v>92886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,11 +1086,11 @@
         <v>128500895</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1185,32 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128500934</v>
+        <v>128501107</v>
       </c>
       <c r="B7" t="n">
-        <v>92456</v>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372572</v>
+        <v>372609</v>
       </c>
       <c r="R7" t="n">
-        <v>7026354</v>
+        <v>7026280</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,108 +1284,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>128501107</v>
-      </c>
-      <c r="B8" t="n">
-        <v>83010</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Högåsen, Högåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>372609</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7026280</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Bördig, löv-och örtrik (bitvis frodig) grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16667-2025 artfynd.xlsx
+++ b/artfynd/A 16667-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501038</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128500925</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128500934</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501302</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128500895</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,8 +1314,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501107</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>